--- a/site/exports/nwpu-sports-department.xlsx
+++ b/site/exports/nwpu-sports-department.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="61.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,8 +569,61 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>王玉岩</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>体育部</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>毕业层次、专业、日期与授位均未知。；赴美学习的接收机构、学位性质与结束日期未知，不因一年制推非学位。；个人导师、正式论文导师、书目未知；运动队助教不当作学术职级。；讲师目录支持姓名分类；门户href未知且未点击，现职未知。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：拳击运动、跆拳道、身体素质；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；来源ID：new-recovery-nwpu-wangyuyan-s001-64249fbccf3b；https://tiyu.nwpu.edu.cn/info/1311/3183.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>原来源入口为官方职业报道（原来源），不作为独立个人主页展示；此分类不表示链接当前不可用。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>官方职业报道（原来源）：https://tiyu.nwpu.edu.cn/info/1311/3183.htm</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
   </hyperlinks>
@@ -584,11 +637,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40.59999999999999" customWidth="1" min="2" max="2"/>
+    <col width="47.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -666,7 +719,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -927,13 +980,283 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>王玉岩</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>graduation_institution_report</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>北京体育大学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>只称毕业；未明确层次、专业、时间或获授学位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://tiyu.nwpu.edu.cn/info/1311/3183.htm</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>王玉岩</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>overseas_study_degree_type_unknown</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>“赴美留学一年”不能直接认定学位或非学位；2019仅来源年份，不推算结束年。美国为目的国家，接收机构未载。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：overseas_study_degree_type_unknown</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://tiyu.nwpu.edu.cn/info/1311/3183.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>王玉岩</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>教师</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（as_of_source_publication）：2022-11-21；来源记载（院系）：体育部</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://tiyu.nwpu.edu.cn/info/1311/3183.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>王玉岩</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>助教</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>北京体育大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>运动队助教原文，不自动转换为大学教学职级。；任职按留存来源表述保留；不据此认证当前人事状态。；来源title_as_source：助教；来源记载（院系）：女子拳击队</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://tiyu.nwpu.edu.cn/info/1311/3183.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>王玉岩</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>助教</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>黑龙江省拳击队</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>无时段，不认定现任。；任职按留存来源表述保留；不据此认证当前人事状态。；来源title_as_source：助教</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://tiyu.nwpu.edu.cn/info/1311/3183.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1233,14 +1556,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="43.4" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="61.59999999999999" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1356,11 +1679,87 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>王玉岩</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwpu-wangyuyan-s001-64249fbccf3b</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://tiyu.nwpu.edu.cn/info/1311/3183.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:14:00Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>王玉岩</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwpu-wangyuyan-s002-8940d0ffc92c</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://tiyu.nwpu.edu.cn/szdw/jsdw/js1.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:14:00Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>nwpu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>西北工业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
